--- a/scenarios/엑셀 결합 데이터.xlsx
+++ b/scenarios/엑셀 결합 데이터.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\MCI_Diffusion\MCI_ADV2\scenarios\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Y:\scenarios\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{813B7636-E166-441C-AA37-5106C7F57B18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79F9269F-7BA7-4AE2-B2DD-D70D65C04F9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1125" yWindow="3375" windowWidth="18810" windowHeight="15345" xr2:uid="{CF92C1C6-8B04-49EC-97E5-D60716126570}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="28800" windowHeight="15345" xr2:uid="{CF92C1C6-8B04-49EC-97E5-D60716126570}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="5" r:id="rId1"/>
@@ -16071,7 +16071,7 @@
         <v>37.4449939</v>
       </c>
       <c r="N178">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O178">
         <f t="shared" si="2"/>
